--- a/stories/arbres/ATOM-TMP.MET.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Myriam ouvre la porte avec papa. Il fait froid. L'air pique les joues. Papa prend le manteau. Myriam enfile le manteau. Le manteau est chaud. Papa dit : froid, manteau. Ils sortent. Plus tard, il pleut. Des gouttes tombent. Papa prend les bottes. Myriam met les bottes. Ses pieds sont au sec. Papa dit : pluie, bottes. Myriam marche. Les bottes font ploc. Elle touche son manteau. Elle touche ses bottes. Froid, manteau. Pluie, bottes. Papa tient sa main. Myriam répète : manteau. Bottes.</t>
+          <t>Myriam ouvre la porte avec papa. Il fait froid. L'air pique les joues. Papa prend le manteau. Myriam enfile le manteau. Le manteau est chaud. Froid, manteau. Ils sortent. Plus tard, il pleut. Des gouttes tombent. Papa prend les bottes. Myriam met les bottes. Ses pieds sont au sec. Pluie, bottes. Myriam marche. Les bottes font ploc. Elle touche son manteau. Elle touche ses bottes. Froid, manteau. Pluie, bottes. Papa tient sa main. Myriam répète : manteau. Bottes.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Myriam ouvre la porte avec papa. Il fait froid. L'air pique les joues. Papa prend le manteau. Myriam enfile le manteau. Le manteau est chaud.
+papa|Froid, manteau. Ils sortent. Plus tard, il pleut. Des gouttes tombent. Papa prend les bottes.
+narrateur|Myriam met les bottes. Ses pieds sont au sec.
+papa|Pluie, bottes.
+narrateur|Myriam marche. Les bottes font ploc. Elle touche son manteau. Elle touche ses bottes. Froid, manteau. Pluie, bottes. Papa tient sa main. Myriam répète : manteau. Bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Il fait froid, puis il pleut. Que met Myriam ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Myriam a mis le manteau. Il faisait froid. Puis les bottes. Il pleuvait. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Myriam rentre. Elle range les bottes.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MET.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Myriam marche. Les bottes font ploc. Elle touche son manteau. Elle touche ses bottes. Froid, manteau. Pluie, bottes. Papa tient sa main. Myriam répète : manteau. Bottes.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Il fait froid, puis il pleut. Que met Myriam ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Myriam a mis le manteau. Il faisait froid. Puis les bottes. Il pleuvait. Papa était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Myriam rentre. Elle range les bottes.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.MET.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Myriam met manteau et bottes</t>
+          <t>La lettre sous l'averse</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël veut poster une lettre. L'averse arrive. La lettre est un peu froissée. Ils la lissent. Elle tombe dans la boîte rouge.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Myriam ouvre la porte avec papa. Il fait froid. L'air pique les joues. Papa prend le manteau. Myriam enfile le manteau. Le manteau est chaud. Froid, manteau. Ils sortent. Plus tard, il pleut. Des gouttes tombent. Papa prend les bottes. Myriam met les bottes. Ses pieds sont au sec. Pluie, bottes. Myriam marche. Les bottes font ploc. Elle touche son manteau. Elle touche ses bottes. Froid, manteau. Pluie, bottes. Papa tient sa main. Myriam répète : manteau. Bottes.</t>
+          <t>Une enveloppe attend près du bol de cerises. Elle est blanche, un peu pliée. Les cerises sont rouges, toutes brillantes. Dehors, l'averse commence sur le toit. Ça sent la poussière mouillée. Raphaël vit ici, avec papa. La table est collante d'un jus. La boîte aux lettres rouge est au portail. On la voit par la fenêtre. Papa, la lettre. Tu veux la poster ? Oui. Il pleut fort, tu entends ? En ce moment, Raphaël prend l'enveloppe. Un coin est froissé. Elle est bizarre. On la lisse ? Raphaël passe la main. Papa aide, tout doux. Le coin se déplie, presque. Bravo. Elle peut partir. L'averse tape plus fort. Papa tend le manteau. Raphaël glisse les bras. Le manteau sent le tissu froid. Mes mains. Dans les poches ? La lettre va dans la grande poche. Elle est à l'abri. Ils ouvrent la porte. L'averse leur pique les joues. Le chemin jusqu'au portail est court. Des flaques déjà. Une gouttière chante à côté. Raphaël marche près de papa. Ses mains restent dans les poches. La poche de la lettre est sèche. La boîte rouge brille sous l'eau. Un oiseau s'est caché dessous. Elle est là. Tu sors la lettre ? Raphaël sort l'enveloppe. Un peu froissée, encore. Pas mouillée. Il lève le rabat de la boîte. La lettre tombe dedans. Toc. Elle est partie. Merci.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Myriam ouvre la porte avec papa. Il fait &lt;emphasis level="moderate"&gt;froid&lt;/emphasis&gt;. L'air pique les joues. Papa prend le manteau. Myriam enfile le manteau. Le manteau est chaud. Papa dit : froid, manteau. Ils sortent. Plus tard, il pleut. Des gouttes tombent. Papa prend les bottes. Myriam met les bottes. Ses pieds sont au sec. Papa dit : pluie, bottes. Myriam marche. Les bottes font ploc. Elle touche son manteau. Elle touche ses bottes. Froid, manteau. Pluie, bottes. Papa tient sa main. Myriam répète : manteau. Bottes.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une enveloppe attend près du bol de cerises. Elle est blanche, un peu pliée. Les cerises sont rouges, toutes brillantes. Dehors, l'averse commence sur le toit. Ça sent la poussière mouillée. Raphaël vit ici, avec papa. La table est collante d'un jus. La boîte aux lettres rouge est au portail. On la voit par la fenêtre. Papa, la lettre. Tu veux la poster ? Oui. Il pleut fort, tu entends ? En ce moment, Raphaël prend l'enveloppe. Un coin est froissé. Elle est bizarre. On la lisse ? Raphaël passe la main. Papa aide, tout doux. Le coin se déplie, presque. Bravo. Elle peut partir. L'averse tape plus fort. Papa tend le manteau. Raphaël glisse les bras. Le manteau sent le tissu froid. Mes mains. Dans les poches ? La lettre va dans la grande poche. Elle est à l'abri. Ils ouvrent la porte. L'averse leur pique les joues. Le chemin jusqu'au portail est court. Des flaques déjà. Une gouttière chante à côté. Raphaël marche près de papa. Ses mains restent dans les poches. La poche de la lettre est sèche. La boîte rouge brille sous l'eau. Un oiseau s'est caché dessous. Elle est là. Tu sors la lettre ? Raphaël sort l'enveloppe. Un peu froissée, encore. Pas mouillée. Il lève le rabat de la boîte. La lettre tombe dedans. Toc. Elle est partie. Merci.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,58 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Myriam ouvre la porte avec papa. Il fait froid. L'air pique les joues. Papa prend le manteau. Myriam enfile le manteau. Le manteau est chaud.
-papa|Froid, manteau. Ils sortent. Plus tard, il pleut. Des gouttes tombent. Papa prend les bottes.
-narrateur|Myriam met les bottes. Ses pieds sont au sec.
-papa|Pluie, bottes.
-narrateur|Myriam marche. Les bottes font ploc. Elle touche son manteau. Elle touche ses bottes. Froid, manteau. Pluie, bottes. Papa tient sa main. Myriam répète : manteau. Bottes.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une enveloppe attend près du bol de cerises.
+narrateur|Elle est blanche, un peu pliée.
+narrateur|Les cerises sont rouges, toutes brillantes.
+narrateur|Dehors, l'averse commence sur le toit.
+narrateur|Ça sent la poussière mouillée.
+narrateur|Raphaël vit ici, avec papa.
+narrateur|La table est collante d'un jus.
+narrateur|La boîte aux lettres rouge est au portail.
+narrateur|On la voit par la fenêtre.
+enfant-m|Papa, la lettre.
+papa|Tu veux la poster ?
+enfant-m|Oui.
+papa|Il pleut fort, tu entends ?
+narrateur|En ce moment, Raphaël prend l'enveloppe.
+narrateur|Un coin est froissé.
+enfant-m|Elle est bizarre.
+papa|On la lisse ?
+narrateur|Raphaël passe la main.
+narrateur|Papa aide, tout doux.
+narrateur|Le coin se déplie, presque.
+papa|Bravo.
+papa|Elle peut partir.
+narrateur|L'averse tape plus fort.
+narrateur|Papa tend le manteau.
+narrateur|Raphaël glisse les bras.
+narrateur|Le manteau sent le tissu froid.
+enfant-m|Mes mains.
+papa|Dans les poches ?
+narrateur|La lettre va dans la grande poche.
+narrateur|Elle est à l'abri.
+narrateur|Ils ouvrent la porte.
+narrateur|L'averse leur pique les joues.
+narrateur|Le chemin jusqu'au portail est court.
+narrateur|Des flaques déjà.
+narrateur|Une gouttière chante à côté.
+narrateur|Raphaël marche près de papa.
+narrateur|Ses mains restent dans les poches.
+narrateur|La poche de la lettre est sèche.
+narrateur|La boîte rouge brille sous l'eau.
+narrateur|Un oiseau s'est caché dessous.
+enfant-m|Elle est là.
+papa|Tu sors la lettre ?
+narrateur|Raphaël sort l'enveloppe.
+narrateur|Un peu froissée, encore.
+narrateur|Pas mouillée.
+narrateur|Il lève le rabat de la boîte.
+narrateur|La lettre tombe dedans.
+enfant-m|Toc.
+papa|Elle est partie.
+papa|Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,12 +1400,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Il fait froid, puis il pleut. Que met Myriam ?</t>
+          <t>Il pleut fort. Que met Raphaël ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Il fait &lt;emphasis level="moderate"&gt;froid&lt;/emphasis&gt;, puis il pleut. Que met Myriam ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Il pleut fort. Que met Raphaël ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1379,7 +1435,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Froid, le manteau. Pluie, les bottes. Que met-on ?</t>
+          <t>Il pleut. Que met Raphaël ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1428,7 +1484,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,10 +1560,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Il fait froid, puis il pleut. Que met Myriam ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Il pleut fort.
+narrateur|Que met Raphaël ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,12 +1588,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Myriam a mis le manteau. Il faisait froid. Puis les bottes. Il pleuvait. Papa était là.</t>
+          <t>Raphaël referme le rabat. La boîte rouge goutte. Elle est dedans. Oui. Au sec. L'averse chante sur le métal. Raphaël pose la main dessus. C'est froid. La lettre a chaud ? Elle est à l'abri. Tu l'as bien lissée. Ils restent un peu. Une cerise d'eau glisse sur la boîte. L'oiseau sous la boîte picore. Puis ils rentrent. Les chaussures font un bruit mou. Le bol de cerises attend encore. J'en prends une ? Oui. Raphaël croque. Le jus est sucré. Il lui reste aux doigts. Dehors, l'averse continue. La fenêtre se voile.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Myriam a mis le manteau. Il faisait &lt;emphasis level="moderate"&gt;froid&lt;/emphasis&gt;. Puis les bottes. Il pleuvait. Papa était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël referme le rabat. La boîte rouge goutte. Elle est dedans. Oui. Au sec. L'averse chante sur le métal. Raphaël pose la main dessus. C'est froid. La lettre a chaud ? Elle est à l'abri. Tu l'as bien lissée. Ils restent un peu. Une cerise d'eau glisse sur la boîte. L'oiseau sous la boîte picore. Puis ils rentrent. Les chaussures font un bruit mou. Le bol de cerises attend encore. J'en prends une ? Oui. Raphaël croque. Le jus est sucré. Il lui reste aux doigts. Dehors, l'averse continue. La fenêtre se voile.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1593,14 +1649,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1676,10 +1732,32 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Myriam a mis le manteau. Il faisait froid. Puis les bottes. Il pleuvait. Papa était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Raphaël referme le rabat.
+narrateur|La boîte rouge goutte.
+enfant-m|Elle est dedans.
+papa|Oui.
+papa|Au sec.
+narrateur|L'averse chante sur le métal.
+narrateur|Raphaël pose la main dessus.
+narrateur|C'est froid.
+enfant-m|La lettre a chaud ?
+papa|Elle est à l'abri.
+papa|Tu l'as bien lissée.
+narrateur|Ils restent un peu.
+narrateur|Une cerise d'eau glisse sur la boîte.
+narrateur|L'oiseau sous la boîte picore.
+narrateur|Puis ils rentrent.
+narrateur|Les chaussures font un bruit mou.
+narrateur|Le bol de cerises attend encore.
+enfant-m|J'en prends une ?
+papa|Oui.
+narrateur|Raphaël croque.
+narrateur|Le jus est sucré.
+narrateur|Il lui reste aux doigts.
+narrateur|Dehors, l'averse continue.
+narrateur|La fenêtre se voile.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,12 +1782,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Myriam rentre. Elle range les bottes.</t>
+          <t>Papa aide à retirer le manteau. Le manteau goutte près de la porte. La lettre a voyagé ? Dans la boîte. Raphaël regarde le bol. L'enveloppe n'y est plus. Il prend une autre cerise. Le noyau est dur, tout petit.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Myriam rentre. Elle range les bottes.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa aide à retirer le manteau. Le manteau goutte près de la porte. La lettre a voyagé ? Dans la boîte. Raphaël regarde le bol. L'enveloppe n'y est plus. Il prend une autre cerise. Le noyau est dur, tout petit.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1765,14 +1843,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1840,10 +1918,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Myriam rentre. Elle range les bottes.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa aide à retirer le manteau.
+narrateur|Le manteau goutte près de la porte.
+papa|La lettre a voyagé ?
+enfant-m|Dans la boîte.
+narrateur|Raphaël regarde le bol.
+narrateur|L'enveloppe n'y est plus.
+narrateur|Il prend une autre cerise.
+narrateur|Le noyau est dur, tout petit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Au portail, la boîte rouge brille. La lettre dort dedans. Le coin n'est presque plus froissé. Toc. Oui. L'averse chante encore sur le métal. L'oiseau a repris le chemin du toit.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Au portail, la boîte rouge brille. La lettre dort dedans. Le coin n'est presque plus froissé. Toc. Oui. L'averse chante encore sur le métal. L'oiseau a repris le chemin du toit.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1929,14 +2013,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2008,10 +2092,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Au portail, la boîte rouge brille.
+narrateur|La lettre dort dedans.
+narrateur|Le coin n'est presque plus froissé.
+enfant-m|Toc.
+papa|Oui.
+narrateur|L'averse chante encore sur le métal.
+narrateur|L'oiseau a repris le chemin du toit.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2157,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MET.001-04.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>entrée de la maison</t>
+          <t>maison puis boîte aux lettres rouge sous l'averse</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Myriam, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
